--- a/ecommerce_backend/notebooks/data/exports/BI_Report.xlsx
+++ b/ecommerce_backend/notebooks/data/exports/BI_Report.xlsx
@@ -453,7 +453,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>61258985</v>
+        <v>54584951</v>
       </c>
     </row>
     <row r="3">
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1748513</v>
+        <v>1565889</v>
       </c>
     </row>
     <row r="4">
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>59510472</v>
+        <v>53019062</v>
       </c>
     </row>
     <row r="5">
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>42944113.13</v>
+        <v>43079360.12</v>
       </c>
     </row>
     <row r="6">
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16566358.87</v>
+        <v>9939701.880000001</v>
       </c>
     </row>
     <row r="7">
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>27.84</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="8">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4364012</v>
+        <v>4366058</v>
       </c>
     </row>
     <row r="9">
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12202346.87</v>
+        <v>5573643.88</v>
       </c>
     </row>
     <row r="10">
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20.5</v>
+        <v>10.51</v>
       </c>
     </row>
   </sheetData>
@@ -584,10 +584,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3403184</v>
+        <v>3221421</v>
       </c>
       <c r="C2" t="n">
-        <v>621973.85</v>
+        <v>278538.06</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
@@ -599,16 +599,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2959937</v>
+        <v>2670766</v>
       </c>
       <c r="C3" t="n">
-        <v>510366.99</v>
+        <v>185902.5</v>
       </c>
       <c r="D3" t="n">
-        <v>-13.02</v>
+        <v>-17.09</v>
       </c>
       <c r="E3" t="n">
-        <v>-17.94</v>
+        <v>-33.26</v>
       </c>
     </row>
     <row r="4">
@@ -618,16 +618,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4360364</v>
+        <v>3975849</v>
       </c>
       <c r="C4" t="n">
-        <v>900512.9399999999</v>
+        <v>432055.78</v>
       </c>
       <c r="D4" t="n">
-        <v>47.31</v>
+        <v>48.87</v>
       </c>
       <c r="E4" t="n">
-        <v>76.44</v>
+        <v>132.41</v>
       </c>
     </row>
     <row r="5">
@@ -637,16 +637,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4511046</v>
+        <v>3839692</v>
       </c>
       <c r="C5" t="n">
-        <v>940440.38</v>
+        <v>404510.87</v>
       </c>
       <c r="D5" t="n">
-        <v>3.46</v>
+        <v>-3.42</v>
       </c>
       <c r="E5" t="n">
-        <v>4.43</v>
+        <v>-6.38</v>
       </c>
     </row>
     <row r="6">
@@ -656,16 +656,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5044218</v>
+        <v>4590620</v>
       </c>
       <c r="C6" t="n">
-        <v>1074822.31</v>
+        <v>526032.4399999999</v>
       </c>
       <c r="D6" t="n">
-        <v>11.82</v>
+        <v>19.56</v>
       </c>
       <c r="E6" t="n">
-        <v>14.29</v>
+        <v>30.04</v>
       </c>
     </row>
     <row r="7">
@@ -675,16 +675,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3851110</v>
+        <v>3379744</v>
       </c>
       <c r="C7" t="n">
-        <v>752422.24</v>
+        <v>313975.53</v>
       </c>
       <c r="D7" t="n">
-        <v>-23.65</v>
+        <v>-26.38</v>
       </c>
       <c r="E7" t="n">
-        <v>-30</v>
+        <v>-40.31</v>
       </c>
     </row>
     <row r="8">
@@ -694,16 +694,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3427241</v>
+        <v>3185912</v>
       </c>
       <c r="C8" t="n">
-        <v>621648.77</v>
+        <v>264859.04</v>
       </c>
       <c r="D8" t="n">
-        <v>-11.01</v>
+        <v>-5.74</v>
       </c>
       <c r="E8" t="n">
-        <v>-17.38</v>
+        <v>-15.64</v>
       </c>
     </row>
     <row r="9">
@@ -713,16 +713,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4893385</v>
+        <v>4116262</v>
       </c>
       <c r="C9" t="n">
-        <v>1036926.84</v>
+        <v>446412.59</v>
       </c>
       <c r="D9" t="n">
-        <v>42.78</v>
+        <v>29.2</v>
       </c>
       <c r="E9" t="n">
-        <v>66.8</v>
+        <v>68.55</v>
       </c>
     </row>
     <row r="10">
@@ -732,16 +732,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5539147</v>
+        <v>5075625</v>
       </c>
       <c r="C10" t="n">
-        <v>1173925.26</v>
+        <v>582653.3199999999</v>
       </c>
       <c r="D10" t="n">
-        <v>13.2</v>
+        <v>23.31</v>
       </c>
       <c r="E10" t="n">
-        <v>13.21</v>
+        <v>30.52</v>
       </c>
     </row>
     <row r="11">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6412480</v>
+        <v>5616914</v>
       </c>
       <c r="C11" t="n">
-        <v>1247399.26</v>
+        <v>520541</v>
       </c>
       <c r="D11" t="n">
-        <v>15.77</v>
+        <v>10.66</v>
       </c>
       <c r="E11" t="n">
-        <v>6.26</v>
+        <v>-10.66</v>
       </c>
     </row>
     <row r="12">
@@ -770,16 +770,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6576137</v>
+        <v>5921854</v>
       </c>
       <c r="C12" t="n">
-        <v>1287473.64</v>
+        <v>567021.36</v>
       </c>
       <c r="D12" t="n">
-        <v>2.55</v>
+        <v>5.43</v>
       </c>
       <c r="E12" t="n">
-        <v>3.21</v>
+        <v>8.93</v>
       </c>
     </row>
     <row r="13">
@@ -789,16 +789,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8532223</v>
+        <v>7424403</v>
       </c>
       <c r="C13" t="n">
-        <v>2034434.39</v>
+        <v>1051141.4</v>
       </c>
       <c r="D13" t="n">
-        <v>29.75</v>
+        <v>25.37</v>
       </c>
       <c r="E13" t="n">
-        <v>58.02</v>
+        <v>85.38</v>
       </c>
     </row>
   </sheetData>
@@ -869,85 +869,85 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E2" t="n">
-        <v>2543540</v>
+        <v>2172358</v>
       </c>
       <c r="F2" t="n">
-        <v>2285562.5</v>
+        <v>1916929.81</v>
       </c>
       <c r="G2" t="n">
-        <v>4.27</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HOME012</t>
+          <t>ELEC011</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Livpure Smart Water Purifier</t>
+          <t>HP 15s Intel Core i3 Laptop</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Home &amp; Kitchen</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="E3" t="n">
-        <v>2202362</v>
+        <v>1890790</v>
       </c>
       <c r="F3" t="n">
-        <v>1999230.11</v>
+        <v>1832835.7</v>
       </c>
       <c r="G3" t="n">
-        <v>3.7</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ELEC011</t>
+          <t>HOME011</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HP 15s Intel Core i3 Laptop</t>
+          <t>Symphony Diet 12T Air Cooler</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Home &amp; Kitchen</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="E4" t="n">
-        <v>2042787</v>
+        <v>1812044</v>
       </c>
       <c r="F4" t="n">
-        <v>1987941.39</v>
+        <v>1590959.09</v>
       </c>
       <c r="G4" t="n">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HOME011</t>
+          <t>HOME005</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Symphony Diet 12T Air Cooler</t>
+          <t>Philips Air Fryer HD9200</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -956,27 +956,27 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="E5" t="n">
-        <v>2000270</v>
+        <v>1619585</v>
       </c>
       <c r="F5" t="n">
-        <v>1780887.56</v>
+        <v>1353424.53</v>
       </c>
       <c r="G5" t="n">
-        <v>3.36</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HOME005</t>
+          <t>HOME012</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Philips Air Fryer HD9200</t>
+          <t>Livpure Smart Water Purifier</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -985,56 +985,56 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="E6" t="n">
-        <v>1895468</v>
+        <v>1504068</v>
       </c>
       <c r="F6" t="n">
-        <v>1627333.9</v>
+        <v>1315179.92</v>
       </c>
       <c r="G6" t="n">
-        <v>3.19</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FASH010</t>
+          <t>FASH015</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Adidas Ultraboost 22 Sneakers</t>
+          <t>Arrow Formal Blazer Men</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fashion &amp; Clothing</t>
+          <t>Grocery &amp; Food</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>129</v>
+        <v>173</v>
       </c>
       <c r="E7" t="n">
-        <v>1767507</v>
+        <v>1348335</v>
       </c>
       <c r="F7" t="n">
-        <v>1505466.86</v>
+        <v>976998.21</v>
       </c>
       <c r="G7" t="n">
-        <v>2.97</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FASH015</t>
+          <t>FASH010</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Arrow Formal Blazer Men</t>
+          <t>Adidas Ultraboost 22 Sneakers</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1043,56 +1043,56 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>185</v>
+        <v>123</v>
       </c>
       <c r="E8" t="n">
-        <v>1542559</v>
+        <v>1339409</v>
       </c>
       <c r="F8" t="n">
-        <v>1166765</v>
+        <v>1075394.98</v>
       </c>
       <c r="G8" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FASH009</t>
+          <t>ELEC002</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Titan Raga Ladies Watch</t>
+          <t>Realme Narzo 70 Pro</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fashion &amp; Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>149</v>
+        <v>30</v>
       </c>
       <c r="E9" t="n">
-        <v>1401434</v>
+        <v>1218719</v>
       </c>
       <c r="F9" t="n">
-        <v>1098767.48</v>
+        <v>1154325.34</v>
       </c>
       <c r="G9" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FASH002</t>
+          <t>FASH009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nike Air Max 270 Running Shoes</t>
+          <t>Titan Raga Ladies Watch</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1101,16 +1101,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="E10" t="n">
-        <v>1313555</v>
+        <v>1198095</v>
       </c>
       <c r="F10" t="n">
-        <v>1092141.24</v>
+        <v>899737.7</v>
       </c>
       <c r="G10" t="n">
-        <v>2.21</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="11">
@@ -1130,16 +1130,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="E11" t="n">
-        <v>1289875</v>
+        <v>1143077</v>
       </c>
       <c r="F11" t="n">
-        <v>1011584.31</v>
+        <v>870477.16</v>
       </c>
       <c r="G11" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
     </row>
   </sheetData>
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2622540</v>
+        <v>2627757</v>
       </c>
     </row>
     <row r="3">
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>186740</v>
+        <v>187588</v>
       </c>
     </row>
     <row r="5">
@@ -1205,7 +1205,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>283648</v>
+        <v>287607</v>
       </c>
     </row>
     <row r="6">
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>134106</v>
+        <v>128902</v>
       </c>
     </row>
     <row r="8">
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>167978</v>
+        <v>165204</v>
       </c>
     </row>
   </sheetData>
@@ -1279,13 +1279,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>3403184</v>
+        <v>3221421</v>
       </c>
       <c r="C2" t="n">
-        <v>4221005</v>
+        <v>3765564</v>
       </c>
       <c r="D2" t="n">
-        <v>-817821</v>
+        <v>-544143</v>
       </c>
     </row>
     <row r="3">
@@ -1293,13 +1293,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>2959937</v>
+        <v>2670766</v>
       </c>
       <c r="C3" t="n">
-        <v>1740862</v>
+        <v>1621580</v>
       </c>
       <c r="D3" t="n">
-        <v>1219075</v>
+        <v>1049186</v>
       </c>
     </row>
     <row r="4">
@@ -1307,13 +1307,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>4360364</v>
+        <v>3975849</v>
       </c>
       <c r="C4" t="n">
-        <v>3780484</v>
+        <v>3566924</v>
       </c>
       <c r="D4" t="n">
-        <v>579880</v>
+        <v>408925</v>
       </c>
     </row>
     <row r="5">
@@ -1321,13 +1321,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>4511046</v>
+        <v>3839692</v>
       </c>
       <c r="C5" t="n">
-        <v>3127204</v>
+        <v>3521670</v>
       </c>
       <c r="D5" t="n">
-        <v>1383842</v>
+        <v>318022</v>
       </c>
     </row>
     <row r="6">
@@ -1335,13 +1335,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>5044218</v>
+        <v>4590620</v>
       </c>
       <c r="C6" t="n">
-        <v>3149078</v>
+        <v>3235496</v>
       </c>
       <c r="D6" t="n">
-        <v>1895140</v>
+        <v>1355124</v>
       </c>
     </row>
     <row r="7">
@@ -1349,13 +1349,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>3851110</v>
+        <v>3379744</v>
       </c>
       <c r="C7" t="n">
-        <v>2932315</v>
+        <v>2941015</v>
       </c>
       <c r="D7" t="n">
-        <v>918795</v>
+        <v>438729</v>
       </c>
     </row>
     <row r="8">
@@ -1363,13 +1363,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>3427241</v>
+        <v>3185912</v>
       </c>
       <c r="C8" t="n">
-        <v>433865</v>
+        <v>451925</v>
       </c>
       <c r="D8" t="n">
-        <v>2993376</v>
+        <v>2733987</v>
       </c>
     </row>
     <row r="9">
@@ -1377,13 +1377,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>4893385</v>
+        <v>4116262</v>
       </c>
       <c r="C9" t="n">
-        <v>1419130</v>
+        <v>1435045</v>
       </c>
       <c r="D9" t="n">
-        <v>3474255</v>
+        <v>2681217</v>
       </c>
     </row>
     <row r="10">
@@ -1391,13 +1391,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>5539147</v>
+        <v>5075625</v>
       </c>
       <c r="C10" t="n">
-        <v>1187885</v>
+        <v>1640435</v>
       </c>
       <c r="D10" t="n">
-        <v>4351262</v>
+        <v>3435190</v>
       </c>
     </row>
     <row r="11">
@@ -1405,13 +1405,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>6412480</v>
+        <v>5616914</v>
       </c>
       <c r="C11" t="n">
-        <v>1161905</v>
+        <v>1279605</v>
       </c>
       <c r="D11" t="n">
-        <v>5250575</v>
+        <v>4337309</v>
       </c>
     </row>
     <row r="12">
@@ -1419,13 +1419,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>6576137</v>
+        <v>5921854</v>
       </c>
       <c r="C12" t="n">
-        <v>511345</v>
+        <v>653075</v>
       </c>
       <c r="D12" t="n">
-        <v>6064792</v>
+        <v>5268779</v>
       </c>
     </row>
     <row r="13">
@@ -1433,13 +1433,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>8532223</v>
+        <v>7424403</v>
       </c>
       <c r="C13" t="n">
-        <v>1220610</v>
+        <v>1112810</v>
       </c>
       <c r="D13" t="n">
-        <v>7311613</v>
+        <v>6311593</v>
       </c>
     </row>
   </sheetData>
@@ -1490,10 +1490,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>71.58</v>
+        <v>71.75</v>
       </c>
       <c r="D2" t="n">
-        <v>60967.68</v>
+        <v>60852.54</v>
       </c>
     </row>
     <row r="3">
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>136.51</v>
+        <v>137.07</v>
       </c>
       <c r="D3" t="n">
-        <v>31967.68</v>
+        <v>31852.54</v>
       </c>
     </row>
     <row r="4">
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>168.06</v>
+        <v>168.88</v>
       </c>
       <c r="D4" t="n">
-        <v>25967.68</v>
+        <v>25852.54</v>
       </c>
     </row>
     <row r="5">
@@ -1544,298 +1544,298 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>194.24</v>
+        <v>195.33</v>
       </c>
       <c r="D5" t="n">
-        <v>22467.68</v>
+        <v>22352.54</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ELEC013</t>
+          <t>HOME012</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lenovo Smart Tab M10 Plus</t>
+          <t>Livpure Smart Water Purifier</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>208.13</v>
+        <v>267</v>
       </c>
       <c r="D6" t="n">
-        <v>20967.68</v>
+        <v>16352.54</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HOME012</t>
+          <t>HOME011</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Livpure Smart Water Purifier</t>
+          <t>Symphony Diet 12T Air Cooler</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>265</v>
+        <v>315.18</v>
       </c>
       <c r="D7" t="n">
-        <v>16467.68</v>
+        <v>13852.54</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HOME006</t>
+          <t>HOME005</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Eureka Forbes Aquaguard Water Purifier</t>
+          <t>Philips Air Fryer HD9200</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>291.56</v>
+        <v>443.14</v>
       </c>
       <c r="D8" t="n">
-        <v>14967.68</v>
+        <v>9852.540000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HOME011</t>
+          <t>FASH010</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Symphony Diet 12T Air Cooler</t>
+          <t>Adidas Ultraboost 22 Sneakers</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>312.44</v>
+        <v>466.83</v>
       </c>
       <c r="D9" t="n">
-        <v>13967.68</v>
+        <v>9352.540000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HOME005</t>
+          <t>FASH014</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Philips Air Fryer HD9200</t>
+          <t>Ray-Ban Wayfarer Sunglasses</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>437.82</v>
+        <v>637.14</v>
       </c>
       <c r="D10" t="n">
-        <v>9967.68</v>
+        <v>6852.54</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FASH010</t>
+          <t>FASH009</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Adidas Ultraboost 22 Sneakers</t>
+          <t>Titan Raga Ladies Watch</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>460.94</v>
+        <v>746.01</v>
       </c>
       <c r="D11" t="n">
-        <v>9467.68</v>
+        <v>5852.54</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ELEC012</t>
+          <t>HLTH008</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Canon PIXMA MG2577s Printer</t>
+          <t>Omron HEM-7120 Digital BP Monitor</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>515.37</v>
+        <v>746.01</v>
       </c>
       <c r="D12" t="n">
-        <v>8467.68</v>
+        <v>5852.54</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FASH002</t>
+          <t>TOYZ001</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nike Air Max 270 Running Shoes</t>
+          <t>LEGO Classic Bricks Creative Box 484pcs</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>547.71</v>
+        <v>746.01</v>
       </c>
       <c r="D13" t="n">
-        <v>7967.68</v>
+        <v>5852.54</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FASH014</t>
+          <t>FASH015</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ray-Ban Wayfarer Sunglasses</t>
+          <t>Arrow Formal Blazer Men</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>626.3200000000001</v>
+        <v>899.75</v>
       </c>
       <c r="D14" t="n">
-        <v>6967.68</v>
+        <v>4852.54</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HLTH008</t>
+          <t>TOYZ005</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Omron HEM-7120 Digital BP Monitor</t>
+          <t>Fisher-Price Baby Activity Gym</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>731.27</v>
+        <v>938.42</v>
       </c>
       <c r="D15" t="n">
-        <v>5967.68</v>
+        <v>4652.54</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TOYZ001</t>
+          <t>SPRT007</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LEGO Classic Bricks Creative Box 484pcs</t>
+          <t>Strauss Adjustable Dumbbell 20kg Pair</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>731.27</v>
+        <v>938.42</v>
       </c>
       <c r="D16" t="n">
-        <v>5967.68</v>
+        <v>4652.54</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FASH009</t>
+          <t>SPRT009</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Titan Raga Ladies Watch</t>
+          <t>SG Cricket Bat English Willow Grade 2</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>731.27</v>
+        <v>1003.1</v>
       </c>
       <c r="D17" t="n">
-        <v>5967.68</v>
+        <v>4352.54</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FASH015</t>
+          <t>AUTO008</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Arrow Formal Blazer Men</t>
+          <t>Steelbird SBH-17 Full Face Helmet</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>878.48</v>
+        <v>1228.99</v>
       </c>
       <c r="D18" t="n">
-        <v>4967.68</v>
+        <v>3552.54</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TOYZ005</t>
+          <t>SPRT004</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fisher-Price Baby Activity Gym</t>
+          <t>Li-Ning Badminton Racket G-Force 3700</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>915.33</v>
+        <v>1384.93</v>
       </c>
       <c r="D19" t="n">
-        <v>4767.68</v>
+        <v>3152.54</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SPRT007</t>
+          <t>HLTH007</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Strauss Adjustable Dumbbell 20kg Pair</t>
+          <t>Dr. Morepen Blood Pressure Monitor BP02</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>915.33</v>
+        <v>1384.93</v>
       </c>
       <c r="D20" t="n">
-        <v>4767.68</v>
+        <v>3152.54</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SPRT009</t>
+          <t>FASH007</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SG Cricket Bat English Willow Grade 2</t>
+          <t>Woodland Casual Leather Shoes</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>976.8</v>
+        <v>1384.93</v>
       </c>
       <c r="D21" t="n">
-        <v>4467.68</v>
+        <v>3152.54</v>
       </c>
     </row>
   </sheetData>
@@ -1849,7 +1849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D107"/>
+  <dimension ref="A1:D95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1895,70 +1895,70 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ELEC004</t>
+          <t>ELEC005</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JBL Tune 520BT Wireless Headphones</t>
+          <t>boAt Rockerz 255 Earphones</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>-79</v>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ELEC005</t>
+          <t>ELEC006</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>boAt Rockerz 255 Earphones</t>
+          <t>Portronics Harmonics Z7 Speaker</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-87</v>
+        <v>-19</v>
       </c>
       <c r="D4" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ELEC006</t>
+          <t>ELEC008</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Portronics Harmonics Z7 Speaker</t>
+          <t>Anker USB-C Fast Charger 65W</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ELEC007</t>
+          <t>ELEC009</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mi 10000mAh Power Bank</t>
+          <t>Logitech M185 Wireless Mouse</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
         <v>25</v>
@@ -1967,142 +1967,142 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ELEC008</t>
+          <t>ELEC010</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Anker USB-C Fast Charger 65W</t>
+          <t>TP-Link TL-WR841N WiFi Router</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-22</v>
+        <v>-37</v>
       </c>
       <c r="D7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ELEC009</t>
+          <t>ELEC011</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Logitech M185 Wireless Mouse</t>
+          <t>HP 15s Intel Core i3 Laptop</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>-9</v>
       </c>
       <c r="D8" t="n">
-        <v>25</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ELEC010</t>
+          <t>ELEC012</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TP-Link TL-WR841N WiFi Router</t>
+          <t>Canon PIXMA MG2577s Printer</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-41</v>
+        <v>-64</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ELEC011</t>
+          <t>FASH003</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HP 15s Intel Core i3 Laptop</t>
+          <t>H&amp;M Basic Oversized T-Shirt</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-9</v>
+        <v>-44</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ELEC012</t>
+          <t>FASH004</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Canon PIXMA MG2577s Printer</t>
+          <t>Puma Classic Hoodie</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-67</v>
+        <v>-95</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ELEC013</t>
+          <t>FASH006</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lenovo Smart Tab M10 Plus</t>
+          <t>Park Avenue Chino Pants</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>-82</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FASH001</t>
+          <t>FASH007</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Levis 511 Slim Fit Jeans</t>
+          <t>Woodland Casual Leather Shoes</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-1</v>
+        <v>-69</v>
       </c>
       <c r="D13" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FASH002</t>
+          <t>FASH008</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nike Air Max 270 Running Shoes</t>
+          <t>Fastrack Analog Wristwatch</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-19</v>
+        <v>-76</v>
       </c>
       <c r="D14" t="n">
         <v>20</v>
@@ -2111,88 +2111,88 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FASH003</t>
+          <t>FASH009</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H&amp;M Basic Oversized T-Shirt</t>
+          <t>Titan Raga Ladies Watch</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-51</v>
+        <v>-94</v>
       </c>
       <c r="D15" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FASH004</t>
+          <t>FASH010</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Puma Classic Hoodie</t>
+          <t>Adidas Ultraboost 22 Sneakers</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-95</v>
+        <v>-73</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FASH005</t>
+          <t>FASH011</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Allen Solly Formal Shirt Men</t>
+          <t>Zara Women Floral Midi Dress</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-24</v>
+        <v>-15</v>
       </c>
       <c r="D17" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FASH006</t>
+          <t>FASH012</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Park Avenue Chino Pants</t>
+          <t>Wildcraft Backpack 30L</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-85</v>
+        <v>-61</v>
       </c>
       <c r="D18" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FASH007</t>
+          <t>FASH013</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Woodland Casual Leather Shoes</t>
+          <t>Skechers Go Walk Slip-on Shoes</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-77</v>
+        <v>-61</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -2201,52 +2201,52 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FASH008</t>
+          <t>FASH014</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fastrack Analog Wristwatch</t>
+          <t>Ray-Ban Wayfarer Sunglasses</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-78</v>
+        <v>-65</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FASH009</t>
+          <t>FASH015</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Titan Raga Ladies Watch</t>
+          <t>Arrow Formal Blazer Men</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-104</v>
+        <v>-138</v>
       </c>
       <c r="D21" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FASH010</t>
+          <t>HOME002</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Adidas Ultraboost 22 Sneakers</t>
+          <t>Butterfly Smart Plus Mixer Grinder</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-79</v>
+        <v>-37</v>
       </c>
       <c r="D22" t="n">
         <v>12</v>
@@ -2255,160 +2255,160 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FASH011</t>
+          <t>HOME003</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Zara Women Floral Midi Dress</t>
+          <t>Milton Thermosteel Bottle 1L</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-22</v>
+        <v>-89</v>
       </c>
       <c r="D23" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FASH012</t>
+          <t>HOME005</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Wildcraft Backpack 30L</t>
+          <t>Philips Air Fryer HD9200</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-66</v>
+        <v>-89</v>
       </c>
       <c r="D24" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FASH013</t>
+          <t>HOME006</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Skechers Go Walk Slip-on Shoes</t>
+          <t>Eureka Forbes Aquaguard Water Purifier</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-65</v>
+        <v>-99</v>
       </c>
       <c r="D25" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FASH014</t>
+          <t>HOME007</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ray-Ban Wayfarer Sunglasses</t>
+          <t>Borosil Vision Glass Set of 6</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-76</v>
+        <v>-125</v>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FASH015</t>
+          <t>HOME009</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Arrow Formal Blazer Men</t>
+          <t>Solimo Microfiber Bedsheet King Size</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-150</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>HOME001</t>
+          <t>HOME010</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Prestige Induction Cooktop PIC 3.0</t>
+          <t>Pigeon Non-stick Cookware Set 3pcs</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-48</v>
+        <v>-45</v>
       </c>
       <c r="D28" t="n">
-        <v>12</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>HOME002</t>
+          <t>HOME011</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Butterfly Smart Plus Mixer Grinder</t>
+          <t>Symphony Diet 12T Air Cooler</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-40</v>
+        <v>-78</v>
       </c>
       <c r="D29" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>HOME003</t>
+          <t>HOME012</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Milton Thermosteel Bottle 1L</t>
+          <t>Livpure Smart Water Purifier</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-100</v>
+        <v>-70</v>
       </c>
       <c r="D30" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>HOME004</t>
+          <t>HOME013</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Hawkins Contura Pressure Cooker 3L</t>
+          <t>Bajaj Non-stick Roti Maker</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-19</v>
+        <v>-25</v>
       </c>
       <c r="D31" t="n">
         <v>20</v>
@@ -2417,1024 +2417,1024 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HOME005</t>
+          <t>HOME014</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Philips Air Fryer HD9200</t>
+          <t>Wonderchef Copper Triply Kadai 24cm</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-97</v>
+        <v>-75</v>
       </c>
       <c r="D32" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>HOME006</t>
+          <t>BEAU001</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Eureka Forbes Aquaguard Water Purifier</t>
+          <t>Lakme Absolute Skin Natural Mousse Foundation</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-107</v>
+        <v>-95</v>
       </c>
       <c r="D33" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>HOME007</t>
+          <t>BEAU002</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Borosil Vision Glass Set of 6</t>
+          <t>Himalaya Moisturizing Aloe Vera Face Wash</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-133</v>
+        <v>-178</v>
       </c>
       <c r="D34" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HOME008</t>
+          <t>BEAU003</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cello Plastic Storage Container Set</t>
+          <t>Biotique Bio Honey Gel Soothing Face Wash</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-114</v>
+        <v>-228</v>
       </c>
       <c r="D35" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>HOME009</t>
+          <t>BEAU004</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Solimo Microfiber Bedsheet King Size</t>
+          <t>Dove Intense Repair Shampoo 650ml</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>-9</v>
+        <v>-103</v>
       </c>
       <c r="D36" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HOME010</t>
+          <t>BEAU005</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Pigeon Non-stick Cookware Set 3pcs</t>
+          <t>Garnier Fructis Hair Fall Repair Conditioner</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-46</v>
+        <v>-181</v>
       </c>
       <c r="D37" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HOME011</t>
+          <t>BEAU006</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Symphony Diet 12T Air Cooler</t>
+          <t>Nivea Men Dark Spot Reduction Cream</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-83</v>
+        <v>-284</v>
       </c>
       <c r="D38" t="n">
-        <v>6</v>
+        <v>55</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HOME012</t>
+          <t>BEAU007</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Livpure Smart Water Purifier</t>
+          <t>Mamaearth Vitamin C Face Serum 30ml</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-82</v>
+        <v>-145</v>
       </c>
       <c r="D39" t="n">
-        <v>5</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>HOME013</t>
+          <t>BEAU008</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Bajaj Non-stick Roti Maker</t>
+          <t>WOW Skin Science Onion Black Seed Oil</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-50</v>
+        <v>-201</v>
       </c>
       <c r="D40" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HOME014</t>
+          <t>BEAU009</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Wonderchef Copper Triply Kadai 24cm</t>
+          <t>Gillette Mach3 Razor with 5 Blades</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-77</v>
+        <v>-109</v>
       </c>
       <c r="D41" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BEAU001</t>
+          <t>BEAU010</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Lakme Absolute Skin Natural Mousse Foundation</t>
+          <t>Plum Goodness E-Luminence Sunscreen SPF 50</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-108</v>
+        <v>-157</v>
       </c>
       <c r="D42" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BEAU002</t>
+          <t>BEAU011</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Himalaya Moisturizing Aloe Vera Face Wash</t>
+          <t>Lotus Herbals Whiteglow Face Mask</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-196</v>
+        <v>-155</v>
       </c>
       <c r="D43" t="n">
-        <v>70</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BEAU003</t>
+          <t>SPRT001</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Biotique Bio Honey Gel Soothing Face Wash</t>
+          <t>Decathlon Domyos Yoga Mat 8mm</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-249</v>
+        <v>-12</v>
       </c>
       <c r="D44" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BEAU004</t>
+          <t>SPRT002</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Dove Intense Repair Shampoo 650ml</t>
+          <t>Cosco Volleyball with Pump</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-139</v>
+        <v>-30</v>
       </c>
       <c r="D45" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BEAU005</t>
+          <t>SPRT003</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Garnier Fructis Hair Fall Repair Conditioner</t>
+          <t>Nivia Carbon Football Size 5</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-202</v>
+        <v>-40</v>
       </c>
       <c r="D46" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BEAU006</t>
+          <t>SPRT004</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nivea Men Dark Spot Reduction Cream</t>
+          <t>Li-Ning Badminton Racket G-Force 3700</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-319</v>
+        <v>-3</v>
       </c>
       <c r="D47" t="n">
-        <v>55</v>
+        <v>18</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BEAU007</t>
+          <t>SPRT005</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Mamaearth Vitamin C Face Serum 30ml</t>
+          <t>Yonex Mavis 350 Shuttlecock Pack of 6</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-168</v>
+        <v>-58</v>
       </c>
       <c r="D48" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BEAU008</t>
+          <t>SPRT006</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>WOW Skin Science Onion Black Seed Oil</t>
+          <t>Adidas Running Track Pants</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-214</v>
+        <v>7</v>
       </c>
       <c r="D49" t="n">
-        <v>30</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BEAU009</t>
+          <t>SPRT007</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Gillette Mach3 Razor with 5 Blades</t>
+          <t>Strauss Adjustable Dumbbell 20kg Pair</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-120</v>
+        <v>-42</v>
       </c>
       <c r="D50" t="n">
-        <v>60</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BEAU010</t>
+          <t>SPRT008</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Plum Goodness E-Luminence Sunscreen SPF 50</t>
+          <t>Boldfit Resistance Bands Set</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-176</v>
+        <v>-88</v>
       </c>
       <c r="D51" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BEAU011</t>
+          <t>SPRT009</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Lotus Herbals Whiteglow Face Mask</t>
+          <t>SG Cricket Bat English Willow Grade 2</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-166</v>
+        <v>-32</v>
       </c>
       <c r="D52" t="n">
-        <v>45</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SPRT001</t>
+          <t>SPRT010</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Decathlon Domyos Yoga Mat 8mm</t>
+          <t>Nivia Storm Football Shoes</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>-64</v>
       </c>
       <c r="D53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SPRT002</t>
+          <t>BOOK001</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Cosco Volleyball with Pump</t>
+          <t>Rich Dad Poor Dad Nepali Edition</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
       <c r="D54" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SPRT003</t>
+          <t>BOOK002</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Nivia Carbon Football Size 5</t>
+          <t>Business Sutras by Devdutt Pattanaik</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>-40</v>
+        <v>-95</v>
       </c>
       <c r="D55" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SPRT004</t>
+          <t>BOOK003</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Li-Ning Badminton Racket G-Force 3700</t>
+          <t>Atomic Habits James Clear</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-18</v>
+        <v>-29</v>
       </c>
       <c r="D56" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SPRT005</t>
+          <t>BOOK004</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Yonex Mavis 350 Shuttlecock Pack of 6</t>
+          <t>Casio FX-991ES Plus Scientific Calculator</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="D57" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SPRT006</t>
+          <t>BOOK005</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Adidas Running Track Pants</t>
+          <t>Faber-Castell Colour Pencil Set 48</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>-15</v>
       </c>
       <c r="D58" t="n">
-        <v>22</v>
+        <v>45</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SPRT007</t>
+          <t>TOYZ001</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Strauss Adjustable Dumbbell 20kg Pair</t>
+          <t>LEGO Classic Bricks Creative Box 484pcs</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-52</v>
+        <v>-9</v>
       </c>
       <c r="D59" t="n">
-        <v>8</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SPRT008</t>
+          <t>TOYZ002</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Boldfit Resistance Bands Set</t>
+          <t>Barbie Fashionista Doll Set</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>-116</v>
+        <v>-26</v>
       </c>
       <c r="D60" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SPRT009</t>
+          <t>TOYZ003</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SG Cricket Bat English Willow Grade 2</t>
+          <t>Hot Wheels 20-Car Gift Pack</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-34</v>
+        <v>13</v>
       </c>
       <c r="D61" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SPRT010</t>
+          <t>TOYZ004</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Nivia Storm Football Shoes</t>
+          <t>Funskool Monopoly Nepal Edition</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-70</v>
+        <v>-12</v>
       </c>
       <c r="D62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BOOK001</t>
+          <t>TOYZ005</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Rich Dad Poor Dad Nepali Edition</t>
+          <t>Fisher-Price Baby Activity Gym</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-10</v>
+        <v>-43</v>
       </c>
       <c r="D63" t="n">
-        <v>60</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BOOK002</t>
+          <t>TOYZ006</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Business Sutras by Devdutt Pattanaik</t>
+          <t>Pampers Active Baby Diapers Large 56pcs</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>-103</v>
+        <v>9</v>
       </c>
       <c r="D64" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BOOK003</t>
+          <t>TOYZ007</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Atomic Habits James Clear</t>
+          <t>Chicco Baby Silicone Spoon Set</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-39</v>
+        <v>-46</v>
       </c>
       <c r="D65" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BOOK004</t>
+          <t>TOYZ008</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Casio FX-991ES Plus Scientific Calculator</t>
+          <t>Intex Inflatable Swimming Pool Kids</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>34</v>
+        <v>-22</v>
       </c>
       <c r="D66" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BOOK005</t>
+          <t>GROC002</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Faber-Castell Colour Pencil Set 48</t>
+          <t>Patanjali Cow Ghee 1 Litre</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-32</v>
+        <v>-252</v>
       </c>
       <c r="D67" t="n">
-        <v>45</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BOOK007</t>
+          <t>GROC003</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Camlin Geometry Box Student</t>
+          <t>Tata Salt 1kg Pack of 5</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-32</v>
+        <v>-210</v>
       </c>
       <c r="D68" t="n">
-        <v>70</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>TOYZ001</t>
+          <t>GROC005</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>LEGO Classic Bricks Creative Box 484pcs</t>
+          <t>Sipradi Premium Basmati Rice 5kg</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-9</v>
+        <v>-174</v>
       </c>
       <c r="D69" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TOYZ002</t>
+          <t>GROC006</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Barbie Fashionista Doll Set</t>
+          <t>Chitwan Gold Tea 500g</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-26</v>
+        <v>-328</v>
       </c>
       <c r="D70" t="n">
-        <v>18</v>
+        <v>60</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>TOYZ003</t>
+          <t>GROC007</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Hot Wheels 20-Car Gift Pack</t>
+          <t>Dabur Honey 500g</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>13</v>
+        <v>-185</v>
       </c>
       <c r="D71" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>TOYZ004</t>
+          <t>GROC008</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Funskool Monopoly Nepal Edition</t>
+          <t>Real Fruit Juice Mixed Pack of 12</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-22</v>
+        <v>-234</v>
       </c>
       <c r="D72" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>TOYZ005</t>
+          <t>GROC010</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Fisher-Price Baby Activity Gym</t>
+          <t>Nescafe Classic Coffee 200g</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-47</v>
+        <v>-282</v>
       </c>
       <c r="D73" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>TOYZ007</t>
+          <t>GROC011</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Chicco Baby Silicone Spoon Set</t>
+          <t>Amul Butter 500g</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-47</v>
+        <v>-205</v>
       </c>
       <c r="D74" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>TOYZ008</t>
+          <t>GROC012</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Intex Inflatable Swimming Pool Kids</t>
+          <t>Maggi 2-Minute Noodles 12 pack</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>-27</v>
+        <v>-306</v>
       </c>
       <c r="D75" t="n">
-        <v>12</v>
+        <v>75</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>GROC002</t>
+          <t>GROC013</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Patanjali Cow Ghee 1 Litre</t>
+          <t>Fortune Soya Chunks 1kg</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-280</v>
+        <v>-196</v>
       </c>
       <c r="D76" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>GROC003</t>
+          <t>GROC014</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Tata Salt 1kg Pack of 5</t>
+          <t>Kissan Mixed Fruit Jam 700g</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-224</v>
+        <v>-325</v>
       </c>
       <c r="D77" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>GROC004</t>
+          <t>HLTH001</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Sunrise Pure Mustard Oil 5 Litre</t>
+          <t>Dabur Chyawanprash 1kg</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-105</v>
+        <v>-142</v>
       </c>
       <c r="D78" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>GROC005</t>
+          <t>HLTH002</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Sipradi Premium Basmati Rice 5kg</t>
+          <t>Zandu Pancharishta Digestive Tonic 450ml</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-189</v>
+        <v>-132</v>
       </c>
       <c r="D79" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>GROC006</t>
+          <t>HLTH004</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Chitwan Gold Tea 500g</t>
+          <t>Ensure Nutrition Powder Vanilla 400g</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>-214</v>
+        <v>-39</v>
       </c>
       <c r="D80" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>GROC007</t>
+          <t>HLTH005</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Dabur Honey 500g</t>
+          <t>Dettol Original Antiseptic Liquid 500ml</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-205</v>
+        <v>-27</v>
       </c>
       <c r="D81" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>GROC008</t>
+          <t>HLTH006</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Real Fruit Juice Mixed Pack of 12</t>
+          <t>Vicks VapoRub 50ml</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-252</v>
+        <v>-65</v>
       </c>
       <c r="D82" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>GROC009</t>
+          <t>HLTH007</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Bhupi Achar Tomato Pickle 400g</t>
+          <t>Dr. Morepen Blood Pressure Monitor BP02</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-327</v>
+        <v>-87</v>
       </c>
       <c r="D83" t="n">
-        <v>55</v>
+        <v>8</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>GROC010</t>
+          <t>HLTH008</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Nescafe Classic Coffee 200g</t>
+          <t>Omron HEM-7120 Digital BP Monitor</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-311</v>
+        <v>-99</v>
       </c>
       <c r="D84" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>GROC011</t>
+          <t>HLTH009</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Amul Butter 500g</t>
+          <t>Accusure Glucometer Complete Kit</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>-221</v>
+        <v>-73</v>
       </c>
       <c r="D85" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>GROC012</t>
+          <t>HLTH010</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Maggi 2-Minute Noodles 12 pack</t>
+          <t>Moov Pain Relief Cream 50g</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-116</v>
+        <v>-197</v>
       </c>
       <c r="D86" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>GROC013</t>
+          <t>HLTH011</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Fortune Soya Chunks 1kg</t>
+          <t>Protinex Original Nutrition Supplement 400g</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>-211</v>
+        <v>-73</v>
       </c>
       <c r="D87" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>GROC014</t>
+          <t>HLTH012</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Kissan Mixed Fruit Jam 700g</t>
+          <t>Himalaya StayFresh Foot Cream</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>-271</v>
+        <v>-240</v>
       </c>
       <c r="D88" t="n">
         <v>40</v>
@@ -3443,342 +3443,126 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>HLTH001</t>
+          <t>AUTO001</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Dabur Chyawanprash 1kg</t>
+          <t>Bosch Ignition Spark Plug Set of 4</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-172</v>
+        <v>-6</v>
       </c>
       <c r="D89" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>HLTH002</t>
+          <t>AUTO002</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Zandu Pancharishta Digestive Tonic 450ml</t>
+          <t>3M Scratch Remover Paste 200g</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>-144</v>
+        <v>-30</v>
       </c>
       <c r="D90" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>HLTH003</t>
+          <t>AUTO004</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Himalaya Ashvagandha General Wellness Tablet</t>
+          <t>Philips H4 Bulb 55W Pair</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>-133</v>
+        <v>3</v>
       </c>
       <c r="D91" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>HLTH004</t>
+          <t>AUTO005</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Ensure Nutrition Powder Vanilla 400g</t>
+          <t>Amaron Pro Bike Battery 12V 5Ah</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>-40</v>
+        <v>-11</v>
       </c>
       <c r="D92" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>HLTH005</t>
+          <t>AUTO006</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Dettol Original Antiseptic Liquid 500ml</t>
+          <t>Motul 7100 Engine Oil 1L 4T 10W40</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>-31</v>
+        <v>-1</v>
       </c>
       <c r="D93" t="n">
-        <v>55</v>
+        <v>18</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>HLTH006</t>
+          <t>AUTO007</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Vicks VapoRub 50ml</t>
+          <t>Vega Evo Open Face Helmet</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-80</v>
+        <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>70</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>HLTH007</t>
+          <t>AUTO008</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Dr. Morepen Blood Pressure Monitor BP02</t>
+          <t>Steelbird SBH-17 Full Face Helmet</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>-89</v>
+        <v>-2</v>
       </c>
       <c r="D95" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>HLTH008</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Omron HEM-7120 Digital BP Monitor</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
-        <v>-109</v>
-      </c>
-      <c r="D96" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>HLTH009</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Accusure Glucometer Complete Kit</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
-        <v>-80</v>
-      </c>
-      <c r="D97" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>HLTH010</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Moov Pain Relief Cream 50g</t>
-        </is>
-      </c>
-      <c r="C98" t="n">
-        <v>-213</v>
-      </c>
-      <c r="D98" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>HLTH011</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Protinex Original Nutrition Supplement 400g</t>
-        </is>
-      </c>
-      <c r="C99" t="n">
-        <v>-79</v>
-      </c>
-      <c r="D99" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>HLTH012</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Himalaya StayFresh Foot Cream</t>
-        </is>
-      </c>
-      <c r="C100" t="n">
-        <v>-204</v>
-      </c>
-      <c r="D100" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>AUTO001</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Bosch Ignition Spark Plug Set of 4</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
-        <v>-9</v>
-      </c>
-      <c r="D101" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>AUTO002</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>3M Scratch Remover Paste 200g</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>-30</v>
-      </c>
-      <c r="D102" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>AUTO004</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Philips H4 Bulb 55W Pair</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
-        <v>0</v>
-      </c>
-      <c r="D103" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>AUTO005</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Amaron Pro Bike Battery 12V 5Ah</t>
-        </is>
-      </c>
-      <c r="C104" t="n">
-        <v>-16</v>
-      </c>
-      <c r="D104" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>AUTO006</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Motul 7100 Engine Oil 1L 4T 10W40</t>
-        </is>
-      </c>
-      <c r="C105" t="n">
-        <v>-1</v>
-      </c>
-      <c r="D105" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>AUTO007</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Vega Evo Open Face Helmet</t>
-        </is>
-      </c>
-      <c r="C106" t="n">
-        <v>-9</v>
-      </c>
-      <c r="D106" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>AUTO008</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Steelbird SBH-17 Full Face Helmet</t>
-        </is>
-      </c>
-      <c r="C107" t="n">
-        <v>-44</v>
-      </c>
-      <c r="D107" t="n">
         <v>10</v>
       </c>
     </row>
